--- a/education_forms/030_student_food_survey_template--education_forms.xlsx
+++ b/education_forms/030_student_food_survey_template--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2129,34 +2129,34 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>food_preferences_taste_choices</t>
+          <t>food_preferences_appearance_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>sour</t>
+          <t>colorful</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Colorful</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>food_preferences_taste_choices</t>
+          <t>food_preferences_appearance_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>salty</t>
+          <t>smelly</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salty</t>
+          <t>Smelly</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>colorful</t>
+          <t>crunchy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Colorful</t>
+          <t>Crunchy</t>
         </is>
       </c>
     </row>
@@ -2185,46 +2185,46 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>smelly</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Smelly</t>
+          <t>Soft</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>food_preferences_appearance_choices</t>
+          <t>eating_habits_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>crunchy</t>
+          <t>eat_quickly</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Crunchy</t>
+          <t>Eat quickly</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>food_preferences_appearance_choices</t>
+          <t>eating_habits_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>soft</t>
+          <t>eat_slowly</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>Eat slowly</t>
         </is>
       </c>
     </row>
@@ -2236,46 +2236,46 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eat_quickly</t>
+          <t>eat_mindfully</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eat quickly</t>
+          <t>Eat mindfully</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>eating_habits_choices</t>
+          <t>food_preferences_price_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>eat_slowly</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eat slowly</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>eating_habits_choices</t>
+          <t>food_preferences_price_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>eat_mindfully</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eat mindfully</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2287,46 +2287,46 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>food_preferences_price_choices</t>
+          <t>favorite_ingredient_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>food_preferences_price_choices</t>
+          <t>favorite_ingredient_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>meat</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>vegetables</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vegetables</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
@@ -2372,44 +2372,10 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fruits</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
-        <is>
-          <t>Fruits</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>favorite_ingredient_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>grains</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Grains</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>favorite_ingredient_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
         <is>
           <t>Dairy</t>
         </is>
